--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -2105,11 +2105,11 @@
         <v>120809105</v>
       </c>
       <c r="B13" t="n">
-        <v>107296</v>
+        <v>107460</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -2105,7 +2105,7 @@
         <v>120809105</v>
       </c>
       <c r="B13" t="n">
-        <v>107460</v>
+        <v>107563</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -2105,7 +2105,7 @@
         <v>120809105</v>
       </c>
       <c r="B13" t="n">
-        <v>107563</v>
+        <v>107571</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -2105,7 +2105,7 @@
         <v>120809105</v>
       </c>
       <c r="B13" t="n">
-        <v>107571</v>
+        <v>107573</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -2105,7 +2105,7 @@
         <v>120809105</v>
       </c>
       <c r="B13" t="n">
-        <v>107573</v>
+        <v>107581</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -2105,7 +2105,7 @@
         <v>120809105</v>
       </c>
       <c r="B13" t="n">
-        <v>107581</v>
+        <v>107585</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2100,135 +2100,6 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>120809105</v>
-      </c>
-      <c r="B13" t="n">
-        <v>107585</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>762</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Hedblomster</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Helichrysum arenarium</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Mosslundavägen, Sk</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>443222</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6204769</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Kristianstad</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Vä</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>M-Kri-1139</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Väglänt</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Tony Svensson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -1580,12 +1580,7 @@
         <v>100852982</v>
       </c>
       <c r="B9" t="n">
-        <v>56599</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57910</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1625,10 +1620,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>443430.0227412013</v>
+        <v>443430</v>
       </c>
       <c r="R9" t="n">
-        <v>6204861.063681602</v>
+        <v>6204862</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -1580,7 +1580,7 @@
         <v>100852982</v>
       </c>
       <c r="B9" t="n">
-        <v>57910</v>
+        <v>57913</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -1580,7 +1580,7 @@
         <v>100852982</v>
       </c>
       <c r="B9" t="n">
-        <v>57913</v>
+        <v>57919</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -1580,7 +1580,7 @@
         <v>100852982</v>
       </c>
       <c r="B9" t="n">
-        <v>57919</v>
+        <v>57920</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -1580,7 +1580,7 @@
         <v>100852982</v>
       </c>
       <c r="B9" t="n">
-        <v>57920</v>
+        <v>57932</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2095,6 +2095,541 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129673849</v>
+      </c>
+      <c r="B13" t="n">
+        <v>107946</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>762</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Hedblomster</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Helichrysum arenarium</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vä 46:10, Sk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>443364</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6204757</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vä</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bettina Ekdahl</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bettina Ekdahl, Marika Stenberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129673879</v>
+      </c>
+      <c r="B14" t="n">
+        <v>107946</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>762</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Hedblomster</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Helichrysum arenarium</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vä 46:10, Sk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>443368</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6204939</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vä</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Tätt bestånd, uppskattat antal</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bettina Ekdahl</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bettina Ekdahl, Marika Stenberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129673854</v>
+      </c>
+      <c r="B15" t="n">
+        <v>107946</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>762</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Hedblomster</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Helichrysum arenarium</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vä 46:10, Sk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>443259</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6204757</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vä</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Bettina Ekdahl</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Bettina Ekdahl, Marika Stenberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129673848</v>
+      </c>
+      <c r="B16" t="n">
+        <v>103051</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>223253</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Etternässla</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Urtica urens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vä 46:10, Sk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>443295</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6204780</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vä</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bettina Ekdahl</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bettina Ekdahl, Marika Stenberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129673847</v>
+      </c>
+      <c r="B17" t="n">
+        <v>107946</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>762</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Hedblomster</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Helichrysum arenarium</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vä 46:10, Sk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>443360</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6204953</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vä</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Bettina Ekdahl</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Bettina Ekdahl, Marika Stenberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -2100,7 +2100,7 @@
         <v>129673849</v>
       </c>
       <c r="B13" t="n">
-        <v>107946</v>
+        <v>107958</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>129673879</v>
       </c>
       <c r="B14" t="n">
-        <v>107946</v>
+        <v>107958</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>129673854</v>
       </c>
       <c r="B15" t="n">
-        <v>107946</v>
+        <v>107958</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>129673848</v>
       </c>
       <c r="B16" t="n">
-        <v>103051</v>
+        <v>103063</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>129673847</v>
       </c>
       <c r="B17" t="n">
-        <v>107946</v>
+        <v>107958</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -2100,7 +2100,7 @@
         <v>129673849</v>
       </c>
       <c r="B13" t="n">
-        <v>107958</v>
+        <v>107959</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>129673879</v>
       </c>
       <c r="B14" t="n">
-        <v>107958</v>
+        <v>107959</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>129673854</v>
       </c>
       <c r="B15" t="n">
-        <v>107958</v>
+        <v>107959</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>129673848</v>
       </c>
       <c r="B16" t="n">
-        <v>103063</v>
+        <v>103064</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>129673847</v>
       </c>
       <c r="B17" t="n">
-        <v>107958</v>
+        <v>107959</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -2100,7 +2100,7 @@
         <v>129673849</v>
       </c>
       <c r="B13" t="n">
-        <v>107959</v>
+        <v>107964</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>129673879</v>
       </c>
       <c r="B14" t="n">
-        <v>107959</v>
+        <v>107964</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>129673854</v>
       </c>
       <c r="B15" t="n">
-        <v>107959</v>
+        <v>107964</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>129673848</v>
       </c>
       <c r="B16" t="n">
-        <v>103064</v>
+        <v>103069</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>129673847</v>
       </c>
       <c r="B17" t="n">
-        <v>107959</v>
+        <v>107964</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -2100,7 +2100,7 @@
         <v>129673849</v>
       </c>
       <c r="B13" t="n">
-        <v>107964</v>
+        <v>107968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>129673879</v>
       </c>
       <c r="B14" t="n">
-        <v>107964</v>
+        <v>107968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>129673854</v>
       </c>
       <c r="B15" t="n">
-        <v>107964</v>
+        <v>107968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>129673848</v>
       </c>
       <c r="B16" t="n">
-        <v>103069</v>
+        <v>103073</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>129673847</v>
       </c>
       <c r="B17" t="n">
-        <v>107964</v>
+        <v>107968</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -2100,7 +2100,7 @@
         <v>129673849</v>
       </c>
       <c r="B13" t="n">
-        <v>107968</v>
+        <v>107970</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>129673879</v>
       </c>
       <c r="B14" t="n">
-        <v>107968</v>
+        <v>107970</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>129673854</v>
       </c>
       <c r="B15" t="n">
-        <v>107968</v>
+        <v>107970</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>129673848</v>
       </c>
       <c r="B16" t="n">
-        <v>103073</v>
+        <v>103075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>129673847</v>
       </c>
       <c r="B17" t="n">
-        <v>107968</v>
+        <v>107970</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -2100,7 +2100,7 @@
         <v>129673849</v>
       </c>
       <c r="B13" t="n">
-        <v>107970</v>
+        <v>107980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>129673879</v>
       </c>
       <c r="B14" t="n">
-        <v>107970</v>
+        <v>107980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>129673854</v>
       </c>
       <c r="B15" t="n">
-        <v>107970</v>
+        <v>107980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>129673848</v>
       </c>
       <c r="B16" t="n">
-        <v>103075</v>
+        <v>103085</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>129673847</v>
       </c>
       <c r="B17" t="n">
-        <v>107970</v>
+        <v>107980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -2100,7 +2100,7 @@
         <v>129673849</v>
       </c>
       <c r="B13" t="n">
-        <v>107980</v>
+        <v>107984</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>129673879</v>
       </c>
       <c r="B14" t="n">
-        <v>107980</v>
+        <v>107984</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>129673854</v>
       </c>
       <c r="B15" t="n">
-        <v>107980</v>
+        <v>107984</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>129673848</v>
       </c>
       <c r="B16" t="n">
-        <v>103085</v>
+        <v>103089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>129673847</v>
       </c>
       <c r="B17" t="n">
-        <v>107980</v>
+        <v>107984</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -2100,7 +2100,7 @@
         <v>129673849</v>
       </c>
       <c r="B13" t="n">
-        <v>107984</v>
+        <v>107987</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>129673879</v>
       </c>
       <c r="B14" t="n">
-        <v>107984</v>
+        <v>107987</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>129673854</v>
       </c>
       <c r="B15" t="n">
-        <v>107984</v>
+        <v>107987</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>129673848</v>
       </c>
       <c r="B16" t="n">
-        <v>103089</v>
+        <v>103092</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>129673847</v>
       </c>
       <c r="B17" t="n">
-        <v>107984</v>
+        <v>107987</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -2100,7 +2100,7 @@
         <v>129673849</v>
       </c>
       <c r="B13" t="n">
-        <v>107987</v>
+        <v>107988</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>129673879</v>
       </c>
       <c r="B14" t="n">
-        <v>107987</v>
+        <v>107988</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>129673854</v>
       </c>
       <c r="B15" t="n">
-        <v>107987</v>
+        <v>107988</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>129673848</v>
       </c>
       <c r="B16" t="n">
-        <v>103092</v>
+        <v>103093</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>129673847</v>
       </c>
       <c r="B17" t="n">
-        <v>107987</v>
+        <v>107988</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -2100,7 +2100,7 @@
         <v>129673849</v>
       </c>
       <c r="B13" t="n">
-        <v>107988</v>
+        <v>108005</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>129673879</v>
       </c>
       <c r="B14" t="n">
-        <v>107988</v>
+        <v>108005</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>129673854</v>
       </c>
       <c r="B15" t="n">
-        <v>107988</v>
+        <v>108005</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>129673848</v>
       </c>
       <c r="B16" t="n">
-        <v>103093</v>
+        <v>103110</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>129673847</v>
       </c>
       <c r="B17" t="n">
-        <v>107988</v>
+        <v>108005</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -2635,7 +2635,7 @@
         <v>130199529</v>
       </c>
       <c r="B18" t="n">
-        <v>108021</v>
+        <v>108024</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>130198462</v>
       </c>
       <c r="B19" t="n">
-        <v>108021</v>
+        <v>108024</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>130198463</v>
       </c>
       <c r="B20" t="n">
-        <v>108021</v>
+        <v>108024</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>130199533</v>
       </c>
       <c r="B21" t="n">
-        <v>108021</v>
+        <v>108024</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3040,45 +3040,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130199525</v>
+        <v>130198460</v>
       </c>
       <c r="B22" t="n">
-        <v>105809</v>
+        <v>101040</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221141</v>
+        <v>222886</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Mill.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>917, Sk</t>
+          <t>1950, Sk</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>443385</v>
+        <v>443387</v>
       </c>
       <c r="R22" t="n">
-        <v>6204816</v>
+        <v>6204846</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3111,6 +3111,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3137,45 +3142,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130198460</v>
+        <v>130199525</v>
       </c>
       <c r="B23" t="n">
-        <v>101038</v>
+        <v>105812</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222886</v>
+        <v>221141</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1950, Sk</t>
+          <t>917, Sk</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443387</v>
+        <v>443385</v>
       </c>
       <c r="R23" t="n">
-        <v>6204846</v>
+        <v>6204816</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3208,11 +3213,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3239,45 +3239,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130200540</v>
+        <v>130199531</v>
       </c>
       <c r="B24" t="n">
-        <v>56673</v>
+        <v>108024</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>208255</v>
+        <v>762</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Helichrysum arenarium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3104, Sk</t>
+          <t>912, Sk</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443343</v>
+        <v>443367</v>
       </c>
       <c r="R24" t="n">
-        <v>6204744</v>
+        <v>6204945</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3310,6 +3310,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Mycket stort antal</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3339,7 +3344,7 @@
         <v>130199526</v>
       </c>
       <c r="B25" t="n">
-        <v>105809</v>
+        <v>105812</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3433,45 +3438,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130199531</v>
+        <v>130200540</v>
       </c>
       <c r="B26" t="n">
-        <v>108021</v>
+        <v>56673</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>762</v>
+        <v>208255</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Helichrysum arenarium</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>912, Sk</t>
+          <t>3104, Sk</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443367</v>
+        <v>443343</v>
       </c>
       <c r="R26" t="n">
-        <v>6204945</v>
+        <v>6204744</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3504,11 +3509,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Mycket stort antal</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -2635,7 +2635,7 @@
         <v>130199529</v>
       </c>
       <c r="B18" t="n">
-        <v>108024</v>
+        <v>108111</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>130198462</v>
       </c>
       <c r="B19" t="n">
-        <v>108024</v>
+        <v>108111</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>130198463</v>
       </c>
       <c r="B20" t="n">
-        <v>108024</v>
+        <v>108111</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>130199533</v>
       </c>
       <c r="B21" t="n">
-        <v>108024</v>
+        <v>108111</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>130198460</v>
       </c>
       <c r="B22" t="n">
-        <v>101040</v>
+        <v>101127</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>130199525</v>
       </c>
       <c r="B23" t="n">
-        <v>105812</v>
+        <v>105899</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>130199531</v>
       </c>
       <c r="B24" t="n">
-        <v>108024</v>
+        <v>108111</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>130199526</v>
       </c>
       <c r="B25" t="n">
-        <v>105812</v>
+        <v>105899</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>130200540</v>
       </c>
       <c r="B26" t="n">
-        <v>56673</v>
+        <v>56758</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>130200490</v>
       </c>
       <c r="B27" t="n">
-        <v>56673</v>
+        <v>56758</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -3040,45 +3040,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130198460</v>
+        <v>130199525</v>
       </c>
       <c r="B22" t="n">
-        <v>101127</v>
+        <v>105899</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222886</v>
+        <v>221141</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1950, Sk</t>
+          <t>917, Sk</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>443387</v>
+        <v>443385</v>
       </c>
       <c r="R22" t="n">
-        <v>6204846</v>
+        <v>6204816</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3111,11 +3111,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3142,45 +3137,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130199525</v>
+        <v>130198460</v>
       </c>
       <c r="B23" t="n">
-        <v>105899</v>
+        <v>101127</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221141</v>
+        <v>222886</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Mill.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>917, Sk</t>
+          <t>1950, Sk</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443385</v>
+        <v>443387</v>
       </c>
       <c r="R23" t="n">
-        <v>6204816</v>
+        <v>6204846</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3213,6 +3208,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -3040,45 +3040,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130199525</v>
+        <v>130198460</v>
       </c>
       <c r="B22" t="n">
-        <v>105899</v>
+        <v>101127</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221141</v>
+        <v>222886</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Mill.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>917, Sk</t>
+          <t>1950, Sk</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>443385</v>
+        <v>443387</v>
       </c>
       <c r="R22" t="n">
-        <v>6204816</v>
+        <v>6204846</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3111,6 +3111,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3137,45 +3142,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130198460</v>
+        <v>130199525</v>
       </c>
       <c r="B23" t="n">
-        <v>101127</v>
+        <v>105899</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222886</v>
+        <v>221141</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1950, Sk</t>
+          <t>917, Sk</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443387</v>
+        <v>443385</v>
       </c>
       <c r="R23" t="n">
-        <v>6204846</v>
+        <v>6204816</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3208,11 +3213,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -3239,45 +3239,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130199531</v>
+        <v>130200540</v>
       </c>
       <c r="B24" t="n">
-        <v>108111</v>
+        <v>56758</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>762</v>
+        <v>208255</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Helichrysum arenarium</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>912, Sk</t>
+          <t>3104, Sk</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443367</v>
+        <v>443343</v>
       </c>
       <c r="R24" t="n">
-        <v>6204945</v>
+        <v>6204744</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3310,11 +3310,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Mycket stort antal</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3341,45 +3336,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130200540</v>
+        <v>130199531</v>
       </c>
       <c r="B25" t="n">
-        <v>56758</v>
+        <v>108111</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>208255</v>
+        <v>762</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Helichrysum arenarium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>3104, Sk</t>
+          <t>912, Sk</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443343</v>
+        <v>443367</v>
       </c>
       <c r="R25" t="n">
-        <v>6204744</v>
+        <v>6204945</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3412,6 +3407,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Mycket stort antal</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -3239,45 +3239,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130200540</v>
+        <v>130199531</v>
       </c>
       <c r="B24" t="n">
-        <v>56758</v>
+        <v>108111</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>208255</v>
+        <v>762</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Helichrysum arenarium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3104, Sk</t>
+          <t>912, Sk</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443343</v>
+        <v>443367</v>
       </c>
       <c r="R24" t="n">
-        <v>6204744</v>
+        <v>6204945</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3310,6 +3310,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Mycket stort antal</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3336,45 +3341,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130199531</v>
+        <v>130200540</v>
       </c>
       <c r="B25" t="n">
-        <v>108111</v>
+        <v>56758</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>762</v>
+        <v>208255</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Helichrysum arenarium</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>912, Sk</t>
+          <t>3104, Sk</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443367</v>
+        <v>443343</v>
       </c>
       <c r="R25" t="n">
-        <v>6204945</v>
+        <v>6204744</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3407,11 +3412,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Mycket stort antal</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -2635,7 +2635,7 @@
         <v>130199529</v>
       </c>
       <c r="B18" t="n">
-        <v>108111</v>
+        <v>108114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>130198462</v>
       </c>
       <c r="B19" t="n">
-        <v>108111</v>
+        <v>108114</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>130198463</v>
       </c>
       <c r="B20" t="n">
-        <v>108111</v>
+        <v>108114</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>130199533</v>
       </c>
       <c r="B21" t="n">
-        <v>108111</v>
+        <v>108114</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>130199525</v>
       </c>
       <c r="B22" t="n">
-        <v>105899</v>
+        <v>105902</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>130198460</v>
       </c>
       <c r="B23" t="n">
-        <v>101127</v>
+        <v>101130</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3239,45 +3239,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130199531</v>
+        <v>130200540</v>
       </c>
       <c r="B24" t="n">
-        <v>108111</v>
+        <v>56758</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>762</v>
+        <v>208255</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Helichrysum arenarium</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>912, Sk</t>
+          <t>3104, Sk</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443367</v>
+        <v>443343</v>
       </c>
       <c r="R24" t="n">
-        <v>6204945</v>
+        <v>6204744</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3310,11 +3310,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Mycket stort antal</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3341,45 +3336,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130200540</v>
+        <v>130199531</v>
       </c>
       <c r="B25" t="n">
-        <v>56758</v>
+        <v>108114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>208255</v>
+        <v>762</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Helichrysum arenarium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>3104, Sk</t>
+          <t>912, Sk</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443343</v>
+        <v>443367</v>
       </c>
       <c r="R25" t="n">
-        <v>6204744</v>
+        <v>6204945</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3412,6 +3407,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Mycket stort antal</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3441,7 +3441,7 @@
         <v>130199526</v>
       </c>
       <c r="B26" t="n">
-        <v>105899</v>
+        <v>105902</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -2635,7 +2635,7 @@
         <v>130199529</v>
       </c>
       <c r="B18" t="n">
-        <v>108114</v>
+        <v>108140</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>130198462</v>
       </c>
       <c r="B19" t="n">
-        <v>108114</v>
+        <v>108140</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>130198463</v>
       </c>
       <c r="B20" t="n">
-        <v>108114</v>
+        <v>108140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>130199533</v>
       </c>
       <c r="B21" t="n">
-        <v>108114</v>
+        <v>108140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3040,45 +3040,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130199525</v>
+        <v>130198460</v>
       </c>
       <c r="B22" t="n">
-        <v>105902</v>
+        <v>101156</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221141</v>
+        <v>222886</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Mill.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>917, Sk</t>
+          <t>1950, Sk</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>443385</v>
+        <v>443387</v>
       </c>
       <c r="R22" t="n">
-        <v>6204816</v>
+        <v>6204846</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3111,6 +3111,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3137,45 +3142,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130198460</v>
+        <v>130199525</v>
       </c>
       <c r="B23" t="n">
-        <v>101130</v>
+        <v>105928</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222886</v>
+        <v>221141</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1950, Sk</t>
+          <t>917, Sk</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443387</v>
+        <v>443385</v>
       </c>
       <c r="R23" t="n">
-        <v>6204846</v>
+        <v>6204816</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3208,11 +3213,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3242,7 +3242,7 @@
         <v>130200540</v>
       </c>
       <c r="B24" t="n">
-        <v>56758</v>
+        <v>56784</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>130199531</v>
       </c>
       <c r="B25" t="n">
-        <v>108114</v>
+        <v>108140</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>130199526</v>
       </c>
       <c r="B26" t="n">
-        <v>105902</v>
+        <v>105928</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>130200490</v>
       </c>
       <c r="B27" t="n">
-        <v>56758</v>
+        <v>56784</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -2635,7 +2635,7 @@
         <v>130199529</v>
       </c>
       <c r="B18" t="n">
-        <v>108140</v>
+        <v>108141</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>130198462</v>
       </c>
       <c r="B19" t="n">
-        <v>108140</v>
+        <v>108141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>130198463</v>
       </c>
       <c r="B20" t="n">
-        <v>108140</v>
+        <v>108141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>130199533</v>
       </c>
       <c r="B21" t="n">
-        <v>108140</v>
+        <v>108141</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3040,45 +3040,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130198460</v>
+        <v>130199525</v>
       </c>
       <c r="B22" t="n">
-        <v>101156</v>
+        <v>105929</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222886</v>
+        <v>221141</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1950, Sk</t>
+          <t>917, Sk</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>443387</v>
+        <v>443385</v>
       </c>
       <c r="R22" t="n">
-        <v>6204846</v>
+        <v>6204816</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3111,11 +3111,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3142,45 +3137,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130199525</v>
+        <v>130198460</v>
       </c>
       <c r="B23" t="n">
-        <v>105928</v>
+        <v>101157</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221141</v>
+        <v>222886</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Mill.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>917, Sk</t>
+          <t>1950, Sk</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443385</v>
+        <v>443387</v>
       </c>
       <c r="R23" t="n">
-        <v>6204816</v>
+        <v>6204846</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3213,6 +3208,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3239,10 +3239,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130200540</v>
+        <v>130199526</v>
       </c>
       <c r="B24" t="n">
-        <v>56784</v>
+        <v>105929</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3250,34 +3250,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>208255</v>
+        <v>221141</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3104, Sk</t>
+          <t>916, Sk</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443343</v>
+        <v>443374</v>
       </c>
       <c r="R24" t="n">
-        <v>6204744</v>
+        <v>6204821</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3339,7 +3339,7 @@
         <v>130199531</v>
       </c>
       <c r="B25" t="n">
-        <v>108140</v>
+        <v>108141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130199526</v>
+        <v>130200540</v>
       </c>
       <c r="B26" t="n">
-        <v>105928</v>
+        <v>56784</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3449,34 +3449,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221141</v>
+        <v>208255</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>916, Sk</t>
+          <t>3104, Sk</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443374</v>
+        <v>443343</v>
       </c>
       <c r="R26" t="n">
-        <v>6204821</v>
+        <v>6204744</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -2635,7 +2635,7 @@
         <v>130199529</v>
       </c>
       <c r="B18" t="n">
-        <v>108141</v>
+        <v>108142</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>130198462</v>
       </c>
       <c r="B19" t="n">
-        <v>108141</v>
+        <v>108142</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>130198463</v>
       </c>
       <c r="B20" t="n">
-        <v>108141</v>
+        <v>108142</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>130199533</v>
       </c>
       <c r="B21" t="n">
-        <v>108141</v>
+        <v>108142</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>130199525</v>
       </c>
       <c r="B22" t="n">
-        <v>105929</v>
+        <v>105930</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>130198460</v>
       </c>
       <c r="B23" t="n">
-        <v>101157</v>
+        <v>101158</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3239,10 +3239,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130199526</v>
+        <v>130200540</v>
       </c>
       <c r="B24" t="n">
-        <v>105929</v>
+        <v>56784</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3250,34 +3250,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221141</v>
+        <v>208255</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>916, Sk</t>
+          <t>3104, Sk</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443374</v>
+        <v>443343</v>
       </c>
       <c r="R24" t="n">
-        <v>6204821</v>
+        <v>6204744</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3336,45 +3336,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130199531</v>
+        <v>130199526</v>
       </c>
       <c r="B25" t="n">
-        <v>108141</v>
+        <v>105930</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>762</v>
+        <v>221141</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Helichrysum arenarium</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>912, Sk</t>
+          <t>916, Sk</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443367</v>
+        <v>443374</v>
       </c>
       <c r="R25" t="n">
-        <v>6204945</v>
+        <v>6204821</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3407,11 +3407,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Mycket stort antal</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3438,45 +3433,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130200540</v>
+        <v>130199531</v>
       </c>
       <c r="B26" t="n">
-        <v>56784</v>
+        <v>108142</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>208255</v>
+        <v>762</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Helichrysum arenarium</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>3104, Sk</t>
+          <t>912, Sk</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443343</v>
+        <v>443367</v>
       </c>
       <c r="R26" t="n">
-        <v>6204744</v>
+        <v>6204945</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3509,6 +3504,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Mycket stort antal</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -2635,7 +2635,7 @@
         <v>130199529</v>
       </c>
       <c r="B18" t="n">
-        <v>108142</v>
+        <v>108144</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>130198462</v>
       </c>
       <c r="B19" t="n">
-        <v>108142</v>
+        <v>108144</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>130198463</v>
       </c>
       <c r="B20" t="n">
-        <v>108142</v>
+        <v>108144</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>130199533</v>
       </c>
       <c r="B21" t="n">
-        <v>108142</v>
+        <v>108144</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>130199525</v>
       </c>
       <c r="B22" t="n">
-        <v>105930</v>
+        <v>105932</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>130198460</v>
       </c>
       <c r="B23" t="n">
-        <v>101158</v>
+        <v>101160</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>130200540</v>
       </c>
       <c r="B24" t="n">
-        <v>56784</v>
+        <v>56786</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3336,45 +3336,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130199526</v>
+        <v>130199531</v>
       </c>
       <c r="B25" t="n">
-        <v>105930</v>
+        <v>108144</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221141</v>
+        <v>762</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Helichrysum arenarium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>916, Sk</t>
+          <t>912, Sk</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443374</v>
+        <v>443367</v>
       </c>
       <c r="R25" t="n">
-        <v>6204821</v>
+        <v>6204945</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3407,6 +3407,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Mycket stort antal</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3433,45 +3438,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130199531</v>
+        <v>130199526</v>
       </c>
       <c r="B26" t="n">
-        <v>108142</v>
+        <v>105932</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>762</v>
+        <v>221141</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Helichrysum arenarium</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>912, Sk</t>
+          <t>916, Sk</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443367</v>
+        <v>443374</v>
       </c>
       <c r="R26" t="n">
-        <v>6204945</v>
+        <v>6204821</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3504,11 +3509,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Mycket stort antal</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3538,7 +3538,7 @@
         <v>130200490</v>
       </c>
       <c r="B27" t="n">
-        <v>56784</v>
+        <v>56786</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -2635,7 +2635,7 @@
         <v>130199529</v>
       </c>
       <c r="B18" t="n">
-        <v>108144</v>
+        <v>108148</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>130198462</v>
       </c>
       <c r="B19" t="n">
-        <v>108144</v>
+        <v>108148</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>130198463</v>
       </c>
       <c r="B20" t="n">
-        <v>108144</v>
+        <v>108148</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>130199533</v>
       </c>
       <c r="B21" t="n">
-        <v>108144</v>
+        <v>108148</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>130199525</v>
       </c>
       <c r="B22" t="n">
-        <v>105932</v>
+        <v>105936</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>130198460</v>
       </c>
       <c r="B23" t="n">
-        <v>101160</v>
+        <v>101164</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3239,45 +3239,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130200540</v>
+        <v>130199531</v>
       </c>
       <c r="B24" t="n">
-        <v>56786</v>
+        <v>108148</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>208255</v>
+        <v>762</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Helichrysum arenarium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3104, Sk</t>
+          <t>912, Sk</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443343</v>
+        <v>443367</v>
       </c>
       <c r="R24" t="n">
-        <v>6204744</v>
+        <v>6204945</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3310,6 +3310,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Mycket stort antal</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3336,45 +3341,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130199531</v>
+        <v>130199526</v>
       </c>
       <c r="B25" t="n">
-        <v>108144</v>
+        <v>105936</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>762</v>
+        <v>221141</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Helichrysum arenarium</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>912, Sk</t>
+          <t>916, Sk</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443367</v>
+        <v>443374</v>
       </c>
       <c r="R25" t="n">
-        <v>6204945</v>
+        <v>6204821</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3407,11 +3412,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Mycket stort antal</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3438,10 +3438,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130199526</v>
+        <v>130200540</v>
       </c>
       <c r="B26" t="n">
-        <v>105932</v>
+        <v>56786</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3449,34 +3449,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221141</v>
+        <v>208255</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>916, Sk</t>
+          <t>3104, Sk</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443374</v>
+        <v>443343</v>
       </c>
       <c r="R26" t="n">
-        <v>6204821</v>
+        <v>6204744</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7165241</v>
+        <v>66738996</v>
       </c>
       <c r="B2" t="n">
-        <v>105311</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>762</v>
+        <v>527</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Sandnejlika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Helichrysum arenarium</t>
+          <t>Dianthus arenarius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vä, Sk</t>
+          <t>Vä boställe, väg M1653, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443345.1358423349</v>
+        <v>443212</v>
       </c>
       <c r="R2" t="n">
-        <v>6204757.017724931</v>
+        <v>6204771</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-05-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-05-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På uppdrag av Trafikverket. Objekt 148</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,72 +766,78 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Ruderatmark, vägslänter</t>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Malmqvist</t>
+          <t>John Rolander Borlid</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Malmqvist</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>John Rolander Borlid, Mats Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62097619</v>
+        <v>66738998</v>
       </c>
       <c r="B3" t="n">
-        <v>84713</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1614</v>
+        <v>527</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grå stjälkröksvamp</t>
+          <t>Sandnejlika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tulostoma kotlabae</t>
+          <t>Dianthus arenarius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pouzar</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vä, ca 500 m SO Helgeandshuset, M1653 Mosslundavägen., Sk</t>
+          <t>Vä boställe, väg M1653, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443227.5804974322</v>
+        <v>443261</v>
       </c>
       <c r="R3" t="n">
-        <v>6204769.191780161</v>
+        <v>6204751</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,28 +867,17 @@
           <t>2016-06-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-06-14</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -902,40 +886,15 @@
           <t>Vägkant</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Sydvänd sandig torr slänt med mkt blottor</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>Mats Lindqvist</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>2016:4</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>Mikael Jeppson</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mats Lindqvist</t>
+          <t>John Rolander Borlid</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mats Lindqvist, John Rolander Borlid</t>
+          <t>John Rolander Borlid, Mats Lindqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -946,62 +905,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66738999</v>
+        <v>7165241</v>
       </c>
       <c r="B4" t="n">
-        <v>29298</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108387</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102685</v>
+        <v>762</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stortapetserarbi</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Megachile lagopoda</t>
+          <t>Helichrysum arenarium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1761)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vä boställe, väg M1653, Sk</t>
+          <t>Vä, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443260.9721504325</v>
+        <v>443345</v>
       </c>
       <c r="R4" t="n">
-        <v>6204750.852446765</v>
+        <v>6204757</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1025,22 +970,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-06-14</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-05-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-06-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-05-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På uppdrag av Trafikverket. Objekt 148</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1052,39 +992,30 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Ruderatmark, vägslänter</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>John Rolander Borlid</t>
+          <t>Andreas Malmqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mats Lindqvist, John Rolander Borlid</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Andreas Malmqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>66738998</v>
+        <v>66738995</v>
       </c>
       <c r="B5" t="n">
-        <v>102499</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108387</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,21 +1023,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>527</v>
+        <v>762</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sandnejlika</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dianthus arenarius</t>
+          <t>Helichrysum arenarium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1125,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443260.9721504325</v>
+        <v>443195</v>
       </c>
       <c r="R5" t="n">
-        <v>6204750.852446765</v>
+        <v>6204777</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1158,19 +1089,9 @@
           <t>2016-06-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2016-06-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,7 +1116,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mats Lindqvist, John Rolander Borlid</t>
+          <t>John Rolander Borlid, Mats Lindqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1206,37 +1127,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66739000</v>
+        <v>66738997</v>
       </c>
       <c r="B6" t="n">
-        <v>29298</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108387</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102685</v>
+        <v>762</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stortapetserarbi</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Megachile lagopoda</t>
+          <t>Helichrysum arenarium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1761)</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1246,7 +1162,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1255,13 +1171,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443287.2031829325</v>
+        <v>443223</v>
       </c>
       <c r="R6" t="n">
-        <v>6204742.116814381</v>
+        <v>6204763</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1288,19 +1204,9 @@
           <t>2016-06-14</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2016-06-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1325,7 +1231,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mats Lindqvist, John Rolander Borlid</t>
+          <t>John Rolander Borlid, Mats Lindqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1336,15 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>94311774</v>
+        <v>66739001</v>
       </c>
       <c r="B7" t="n">
-        <v>56599</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108387</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,49 +1253,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100124</v>
+        <v>762</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Backsvala</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Riparia riparia</t>
+          <t>Helichrysum arenarium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gamla täkten, Sk</t>
+          <t>Vä boställe, väg M1653, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>443399.5266390729</v>
+        <v>443300</v>
       </c>
       <c r="R7" t="n">
-        <v>6204801.05289479</v>
+        <v>6204712</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1418,22 +1316,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1444,31 +1332,35 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Pontus Olsson</t>
+          <t>John Rolander Borlid</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Pontus Olsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>John Rolander Borlid, Mats Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>96372816</v>
       </c>
       <c r="B8" t="n">
-        <v>105311</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108387</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>443363.724847785</v>
+        <v>443364</v>
       </c>
       <c r="R8" t="n">
-        <v>6204934.649717041</v>
+        <v>6204934</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1537,19 +1429,9 @@
           <t>2021-04-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-04-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1577,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>100852982</v>
+        <v>105343994</v>
       </c>
       <c r="B9" t="n">
-        <v>57932</v>
+        <v>108387</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,45 +1470,53 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100124</v>
+        <v>762</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Backsvala</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Riparia riparia</t>
+          <t>Helichrysum arenarium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Södergård, Vää, Sk</t>
+          <t>Mosslundavägen, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>443430</v>
+        <v>443222</v>
       </c>
       <c r="R9" t="n">
-        <v>6204862</v>
+        <v>6204769</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1650,27 +1540,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-05-15</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>21:00</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-05-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>21:00</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I stor avkapad jordhög, sedd från motorvägen.</t>
+          <t>85 blommande stänglar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1679,33 +1559,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Andersson</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johan Andersson</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104065348</v>
+        <v>105344008</v>
       </c>
       <c r="B10" t="n">
-        <v>28960</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108387</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,47 +1594,50 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102664</v>
+        <v>762</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rapssandbi</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Andrena bimaculata</t>
+          <t>Helichrysum arenarium</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kirby, 1802)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vää grustag, Mosslunda, Sk</t>
+          <t>Mosslundavägen, Sk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443437.4962690717</v>
+        <v>443194</v>
       </c>
       <c r="R10" t="n">
-        <v>6204704.342924918</v>
+        <v>6204779</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1780,27 +1664,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ett tiotal svärmade vid tall</t>
+          <t>60 blommande stänglar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1813,85 +1687,77 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Olle Högmo</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Olle Högmo</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104065224</v>
+        <v>129673846</v>
       </c>
       <c r="B11" t="n">
-        <v>28953</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108386</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103115</v>
+        <v>762</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Alvarsandbi</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Andrena alfkenella</t>
+          <t>Helichrysum arenarium</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>R.C.L.Perkins, 1914</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vää grustag, Mosslunda, Sk</t>
+          <t>Vä 46:10, Sk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443437.4962690717</v>
+        <v>443266</v>
       </c>
       <c r="R11" t="n">
-        <v>6204704.342924918</v>
+        <v>6204743</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1915,22 +1781,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1939,34 +1795,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Olle Högmo</t>
+          <t>Bettina Ekdahl</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Olle Högmo</t>
+          <t>Bettina Ekdahl, Marika Stenberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105343994</v>
+        <v>129673847</v>
       </c>
       <c r="B12" t="n">
-        <v>105311</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108386</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1993,34 +1843,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mosslundavägen, Sk</t>
+          <t>Vä 46:10, Sk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443221.9686129652</v>
+        <v>443360</v>
       </c>
       <c r="R12" t="n">
-        <v>6204768.706295421</v>
+        <v>6204953</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2044,27 +1887,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>85 blommande stänglar.</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2073,24 +1901,18 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Bettina Ekdahl</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Bettina Ekdahl, Marika Stenberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2100,7 +1922,7 @@
         <v>129673849</v>
       </c>
       <c r="B13" t="n">
-        <v>108005</v>
+        <v>108386</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2203,10 +2025,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129673879</v>
+        <v>129673850</v>
       </c>
       <c r="B14" t="n">
-        <v>108005</v>
+        <v>108386</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2233,26 +2055,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vä 46:10, Sk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443368</v>
+        <v>443219</v>
       </c>
       <c r="R14" t="n">
-        <v>6204939</v>
+        <v>6204768</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2284,18 +2107,12 @@
           <t>2025-09-17</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Tätt bestånd, uppskattat antal</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2314,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129673854</v>
+        <v>129673851</v>
       </c>
       <c r="B15" t="n">
-        <v>108005</v>
+        <v>108386</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2344,7 +2161,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2358,10 +2175,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443259</v>
+        <v>443192</v>
       </c>
       <c r="R15" t="n">
-        <v>6204757</v>
+        <v>6204780</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2420,37 +2237,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129673848</v>
+        <v>129673852</v>
       </c>
       <c r="B16" t="n">
-        <v>103110</v>
+        <v>108386</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>223253</v>
+        <v>762</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Etternässla</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Urtica urens</t>
+          <t>Helichrysum arenarium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2464,10 +2281,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443295</v>
+        <v>443196</v>
       </c>
       <c r="R16" t="n">
-        <v>6204780</v>
+        <v>6204779</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2526,10 +2343,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129673847</v>
+        <v>129673853</v>
       </c>
       <c r="B17" t="n">
-        <v>108005</v>
+        <v>108386</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2556,7 +2373,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2570,10 +2387,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>443360</v>
+        <v>443206</v>
       </c>
       <c r="R17" t="n">
-        <v>6204953</v>
+        <v>6204775</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2632,10 +2449,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130199529</v>
+        <v>129673854</v>
       </c>
       <c r="B18" t="n">
-        <v>108148</v>
+        <v>108386</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2660,17 +2477,26 @@
           <t>(L.) Moench</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>913, Sk</t>
+          <t>Vä 46:10, Sk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>443364</v>
+        <v>443259</v>
       </c>
       <c r="R18" t="n">
-        <v>6204927</v>
+        <v>6204757</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2697,17 +2523,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Flera</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2722,22 +2543,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Otto Minas</t>
+          <t>Bettina Ekdahl</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Otto Minas</t>
+          <t>Bettina Ekdahl, Marika Stenberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130198462</v>
+        <v>129673879</v>
       </c>
       <c r="B19" t="n">
-        <v>108148</v>
+        <v>108386</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2762,20 +2583,28 @@
           <t>(L.) Moench</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1948, Sk</t>
+          <t>Vä 46:10, Sk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443396</v>
+        <v>443368</v>
       </c>
       <c r="R19" t="n">
-        <v>6204825</v>
+        <v>6204939</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2799,17 +2628,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Stort antal</t>
+          <t>Tätt bestånd, uppskattat antal</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2818,28 +2647,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Otto Minas</t>
+          <t>Bettina Ekdahl</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Otto Minas</t>
+          <t>Bettina Ekdahl, Marika Stenberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130198463</v>
+        <v>130198462</v>
       </c>
       <c r="B20" t="n">
-        <v>108148</v>
+        <v>108386</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2867,14 +2697,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1947, Sk</t>
+          <t>1948, Sk</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>443413</v>
+        <v>443396</v>
       </c>
       <c r="R20" t="n">
-        <v>6204819</v>
+        <v>6204825</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2911,7 +2741,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Flera</t>
+          <t>Stort antal</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2938,10 +2768,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130199533</v>
+        <v>130198463</v>
       </c>
       <c r="B21" t="n">
-        <v>108148</v>
+        <v>108386</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2969,14 +2799,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>910, Sk</t>
+          <t>1947, Sk</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>443370</v>
+        <v>443413</v>
       </c>
       <c r="R21" t="n">
-        <v>6204951</v>
+        <v>6204819</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3040,45 +2870,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130199525</v>
+        <v>130199529</v>
       </c>
       <c r="B22" t="n">
-        <v>105936</v>
+        <v>108386</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221141</v>
+        <v>762</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Helichrysum arenarium</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>917, Sk</t>
+          <t>913, Sk</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>443385</v>
+        <v>443364</v>
       </c>
       <c r="R22" t="n">
-        <v>6204816</v>
+        <v>6204927</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3111,6 +2941,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Flera</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3137,10 +2972,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130198460</v>
+        <v>130199531</v>
       </c>
       <c r="B23" t="n">
-        <v>101164</v>
+        <v>108386</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,34 +2983,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222886</v>
+        <v>762</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Helichrysum arenarium</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Mill.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1950, Sk</t>
+          <t>912, Sk</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443387</v>
+        <v>443367</v>
       </c>
       <c r="R23" t="n">
-        <v>6204846</v>
+        <v>6204945</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3212,7 +3047,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Mycket stort antal</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3239,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130199531</v>
+        <v>130199533</v>
       </c>
       <c r="B24" t="n">
-        <v>108148</v>
+        <v>108386</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3270,14 +3105,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>912, Sk</t>
+          <t>910, Sk</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443367</v>
+        <v>443370</v>
       </c>
       <c r="R24" t="n">
-        <v>6204945</v>
+        <v>6204951</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3314,7 +3149,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Mycket stort antal</t>
+          <t>Flera</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3341,48 +3176,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130199526</v>
+        <v>62097619</v>
       </c>
       <c r="B25" t="n">
-        <v>105936</v>
+        <v>86925</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221141</v>
+        <v>1614</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Grå stjälkröksvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Tulostoma kotlabae</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>916, Sk</t>
+          <t>Vä, ca 500 m SO Helgeandshuset, M1653 Mosslundavägen., Sk</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443374</v>
+        <v>443228</v>
       </c>
       <c r="R25" t="n">
-        <v>6204821</v>
+        <v>6204769</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3406,12 +3243,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3420,63 +3257,110 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Sydvänd sandig torr slänt med mkt blottor</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>Mats Lindqvist</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>2016:4</t>
+        </is>
+      </c>
       <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>Mikael Jeppson</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Otto Minas</t>
+          <t>Mats Lindqvist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Otto Minas</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Mats Lindqvist, John Rolander Borlid</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130200540</v>
+        <v>94311774</v>
       </c>
       <c r="B26" t="n">
-        <v>56786</v>
+        <v>58203</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>208255</v>
+        <v>100124</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Backsvala</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Riparia riparia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>3104, Sk</t>
+          <t>Gamla täkten, Sk</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443343</v>
+        <v>443400</v>
       </c>
       <c r="R26" t="n">
-        <v>6204744</v>
+        <v>6204801</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3503,12 +3387,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3523,60 +3417,68 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Otto Minas</t>
+          <t>Pontus Olsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Otto Minas</t>
+          <t>Pontus Olsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130200490</v>
+        <v>100852982</v>
       </c>
       <c r="B27" t="n">
-        <v>56786</v>
+        <v>58203</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>208255</v>
+        <v>100124</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Backsvala</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Riparia riparia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>3153, Sk</t>
+          <t>Södergård, Vää, Sk</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443310</v>
+        <v>443430</v>
       </c>
       <c r="R27" t="n">
-        <v>6204761</v>
+        <v>6204862</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3600,17 +3502,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2022-05-15</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2022-05-15</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Fåtal</t>
+          <t>I stor avkapad jordhög, sedd från motorvägen.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3625,15 +3537,944 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
+          <t>Johan Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Johan Andersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>104065348</v>
+      </c>
+      <c r="B28" t="n">
+        <v>29338</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>102664</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Rapssandbi</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Andrena bimaculata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Kirby, 1802)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Vää grustag, Mosslunda, Sk</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>443437</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6204704</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Vä</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>ett tiotal svärmade vid tall</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Olle Högmo</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Olle Högmo</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130200490</v>
+      </c>
+      <c r="B29" t="n">
+        <v>56884</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>3153, Sk</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>443310</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6204761</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Vä</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Fåtal</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
           <t>Otto Minas</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
+      <c r="AX29" t="inlineStr">
         <is>
           <t>Otto Minas</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130200540</v>
+      </c>
+      <c r="B30" t="n">
+        <v>56884</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>3104, Sk</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>443343</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6204744</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Vä</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Otto Minas</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Otto Minas</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130199525</v>
+      </c>
+      <c r="B31" t="n">
+        <v>106155</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>917, Sk</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>443385</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6204816</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Vä</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Otto Minas</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Otto Minas</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130199526</v>
+      </c>
+      <c r="B32" t="n">
+        <v>106155</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>916, Sk</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>443374</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6204821</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Vä</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Otto Minas</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Otto Minas</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129673844</v>
+      </c>
+      <c r="B33" t="n">
+        <v>107516</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Vä 46:10, Sk</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>443196</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6204772</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Vä</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Bettina Ekdahl</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Bettina Ekdahl, Marika Stenberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129673845</v>
+      </c>
+      <c r="B34" t="n">
+        <v>107516</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Vä 46:10, Sk</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>443199</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6204772</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Vä</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Bettina Ekdahl</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Bettina Ekdahl, Marika Stenberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>130198460</v>
+      </c>
+      <c r="B35" t="n">
+        <v>101345</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>222886</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Backsippa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Pulsatilla vulgaris</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>1950, Sk</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>443387</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6204846</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Vä</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Otto Minas</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Otto Minas</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129673848</v>
+      </c>
+      <c r="B36" t="n">
+        <v>103450</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>223253</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Etternässla</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Urtica urens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Vä 46:10, Sk</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>443295</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6204780</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Vä</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Bettina Ekdahl</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Bettina Ekdahl, Marika Stenberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2719-2025 artfynd.xlsx
+++ b/artfynd/A 2719-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66738996</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66738998</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7165241</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66738995</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1239,6 +1264,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66738997</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1352,6 +1382,11 @@
       <c r="AY7" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66739001</t>
         </is>
       </c>
     </row>
@@ -1456,6 +1491,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96372816</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1580,6 +1620,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343994</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1704,6 +1749,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105344008</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1810,6 +1860,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129673846</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1916,6 +1971,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129673847</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2022,6 +2082,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129673849</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2128,6 +2193,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129673850</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2234,6 +2304,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129673851</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2340,6 +2415,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129673852</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2446,6 +2526,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129673853</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2552,6 +2637,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129673854</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2663,6 +2753,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129673879</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2765,6 +2860,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130198462</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2867,6 +2967,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130198463</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2969,6 +3074,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130199529</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3071,6 +3181,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130199531</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3173,6 +3288,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130199533</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3307,6 +3427,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62097619</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3426,6 +3551,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94311774</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3546,6 +3676,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100852982</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3662,6 +3797,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104065348</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3764,6 +3904,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130200490</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3861,6 +4006,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130200540</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3958,6 +4108,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130199525</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4055,6 +4210,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130199526</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4161,6 +4321,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129673844</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4267,6 +4432,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129673845</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4369,6 +4539,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130198460</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4475,8 +4650,50 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129673848</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>